--- a/03_Outputs/Area_Metropolitana/05_Economia/economia.xlsx
+++ b/03_Outputs/Area_Metropolitana/05_Economia/economia.xlsx
@@ -12910,10 +12910,8 @@
       <c r="F16" s="118">
         <v>7.50380806234962</v>
       </c>
-      <c r="G16" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G16" s="120">
+        <v>0.00203917117710659</v>
       </c>
       <c r="H16" s="122">
         <v>392.111265935155</v>
@@ -13328,7 +13326,7 @@
         <v>341.766572516129</v>
       </c>
       <c r="G23" s="121">
-        <v>20.0786628130903</v>
+        <v>20.0807019842674</v>
       </c>
       <c r="H23" s="123">
         <v>16269.058240075</v>
@@ -13563,10 +13561,8 @@
       <c r="F27" s="118">
         <v>6.77559987256938</v>
       </c>
-      <c r="G27" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G27" s="120">
+        <v>0.00421278203899164</v>
       </c>
       <c r="H27" s="122">
         <v>334.903728453785</v>
@@ -13981,7 +13977,7 @@
         <v>349.245026084739</v>
       </c>
       <c r="G34" s="121">
-        <v>11.1879191388365</v>
+        <v>11.1921319208755</v>
       </c>
       <c r="H34" s="123">
         <v>15595.9642294597</v>
@@ -14216,10 +14212,8 @@
       <c r="F38" s="118">
         <v>8.53494935433064</v>
       </c>
-      <c r="G38" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G38" s="120">
+        <v>0.0017298229848521</v>
       </c>
       <c r="H38" s="122">
         <v>338.722068913876</v>
@@ -14634,7 +14628,7 @@
         <v>365.335097664726</v>
       </c>
       <c r="G45" s="121">
-        <v>20.2104797376291</v>
+        <v>20.212209560614</v>
       </c>
       <c r="H45" s="123">
         <v>15993.3031933546</v>
@@ -15043,10 +15037,8 @@
       <c r="E52" s="142">
         <v>2019</v>
       </c>
-      <c r="F52" s="118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F52" s="118">
+        <v>0.0958739713853089</v>
       </c>
       <c r="G52" s="120">
         <v>0.312112169185215</v>
@@ -15284,7 +15276,7 @@
         <v>2019</v>
       </c>
       <c r="F56" s="119">
-        <v>337.842987424109</v>
+        <v>337.938861395495</v>
       </c>
       <c r="G56" s="121">
         <v>47.2826499298558</v>
@@ -16409,10 +16401,8 @@
       <c r="F75" s="118">
         <v>4.90117129582625</v>
       </c>
-      <c r="G75" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G75" s="120">
+        <v>0.00000592971162030594</v>
       </c>
       <c r="H75" s="122">
         <v>849.819949736401</v>
@@ -16591,7 +16581,7 @@
         <v>375.731442467872</v>
       </c>
       <c r="G78" s="121">
-        <v>58.0723262836168</v>
+        <v>58.0723322133284</v>
       </c>
       <c r="H78" s="123">
         <v>16456.8399631041</v>
@@ -16826,10 +16816,8 @@
       <c r="F82" s="118">
         <v>10.4561639546404</v>
       </c>
-      <c r="G82" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G82" s="120">
+        <v>0.0483771499642326</v>
       </c>
       <c r="H82" s="122">
         <v>603.48023714019</v>
@@ -17064,10 +17052,8 @@
       <c r="F86" s="118">
         <v>4.78048134745707</v>
       </c>
-      <c r="G86" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G86" s="120">
+        <v>0.0000075784887294422</v>
       </c>
       <c r="H86" s="122">
         <v>942.605709413376</v>
@@ -17246,7 +17232,7 @@
         <v>339.342265240721</v>
       </c>
       <c r="G89" s="121">
-        <v>33.5951716696174</v>
+        <v>33.6435563980704</v>
       </c>
       <c r="H89" s="123">
         <v>17839.3308562437</v>
@@ -18073,10 +18059,8 @@
       <c r="F103" s="118">
         <v>52.6450750922466</v>
       </c>
-      <c r="G103" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G103" s="120">
+        <v>0.0563134177915688</v>
       </c>
       <c r="H103" s="122">
         <v>237.506580852996</v>
@@ -18193,10 +18177,8 @@
       <c r="F105" s="118">
         <v>12.6565842639132</v>
       </c>
-      <c r="G105" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G105" s="120">
+        <v>0.000403264074089067</v>
       </c>
       <c r="H105" s="122">
         <v>1373.82123471486</v>
@@ -18552,7 +18534,7 @@
         <v>402.63698498189</v>
       </c>
       <c r="G111" s="121">
-        <v>10.847783787341</v>
+        <v>10.9045004692066</v>
       </c>
       <c r="H111" s="123">
         <v>16382.2332970357</v>
@@ -22177,7 +22159,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>10.847783787341</v>
+        <v>10.9045004692066</v>
       </c>
     </row>
     <row r="4">
